--- a/data/trans_orig/IP74A1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP74A1_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto la hipoteca en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de la hipoteca en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>16388</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
